--- a/public/samples/sample_bulk_stock_upload.xlsx
+++ b/public/samples/sample_bulk_stock_upload.xlsx
@@ -453,8 +453,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v/>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2" t="str">
         <v>VIMPIX</v>
@@ -519,7 +519,7 @@
         <v/>
       </c>
       <c r="E3" t="str">
-        <v>MANGO</v>
+        <v/>
       </c>
       <c r="F3" t="str">
         <v>2X5</v>
@@ -559,8 +559,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v/>
+      <c r="A4">
+        <v>2</v>
       </c>
       <c r="B4" t="str">
         <v>VIMPIX</v>
@@ -625,7 +625,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>FOOTBALL</v>
+        <v/>
       </c>
       <c r="F5" t="str">
         <v>7X10</v>
